--- a/Fase 2/Evidencias Grupales/13_Release_Plan_CitaJusta.xlsx
+++ b/Fase 2/Evidencias Grupales/13_Release_Plan_CitaJusta.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Plan" sheetId="1" r:id="Re050cdfba03f4baf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Release" sheetId="2" r:id="R83d7a23aa2144998"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Plan" sheetId="1" r:id="R23cf889730534ce8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Release" sheetId="2" r:id="R9ac9d1544c42461a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -176,130 +176,79 @@
     <x:t xml:space="preserve">HU-004/005/006; Auth; AgendaSlot; catálogos; PostgreSQL; apps/web; cliente HTTP centralizado; PR #43.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">R0.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sprint 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Motor de reasignación</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Candidatos, ranking, ofertas, expiración, aceptación/rechazo y reasignación</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">R0.7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sprint 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reportes y aplicación institucional</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dashboard, reportes, auditoría visible y aplicación Tauri funcional</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Aplicación de escritorio consume API y permite operación institucional principal</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">APIs de negocio y auditoría suficientes</x:t>
+    <x:t xml:space="preserve">Criterios de interpretación del estado</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Entregable principal del Sprint disponible y verificable.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mayor parte del objetivo implementada; quedan cierres/evidencias.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Parte relevante implementada, pero faltan componentes obligatorios.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Pendiente</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Trabajo aún no iniciado funcionalmente.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nota</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Los estados no equivalen a porcentaje académico oficial.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">En progreso</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sprint activo con entregables verificables ya completados y trabajo planificado aún pendiente.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Indicador</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Valor</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Estado</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cantidad</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ruta de releases</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Análisis y arquitectura</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">→</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base del proyecto</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Web creada; desktop/Docker pendientes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Auth / RBAC operativos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">8/8 tareas + E2E 1/1 + Burndown</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Citas y espera</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">R1.0</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Cierre MVP</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Sprint 8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cierre MVP y preparación de defensa</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Web + escritorio + backend + BD + Docker + pruebas + documentación + presentación</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Pendiente</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MVP end-to-end demostrable y entregables académicos completos</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cierre de Sprints anteriores</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Release académica final del proyecto.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Criterios de interpretación del estado</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Entregable principal del Sprint disponible y verificable.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Mayor parte del objetivo implementada; quedan cierres/evidencias.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Parte relevante implementada, pero faltan componentes obligatorios.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Trabajo aún no iniciado funcionalmente.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Nota</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Los estados no equivalen a porcentaje académico oficial.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">En progreso</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sprint activo con entregables verificables ya completados y trabajo planificado aún pendiente.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Indicador</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Valor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Estado</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cantidad</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Ruta de releases</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Análisis y arquitectura</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">→</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base del proyecto</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Web creada; desktop/Docker pendientes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Auth / RBAC operativos</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">8/8 tareas + E2E 1/1 + Burndown</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Citas y espera</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reasignación</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reportes + escritorio</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cierre MVP</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Último avance incorporado</x:t>
@@ -796,7 +745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1b1c910cb5c04e52"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R14d8c3c906514c25"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1045,7 +994,7 @@
     </x:row>
     <x:row r="2" ht="39.75" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Versión 1.5 · Fecha de corte: 20-09-2026 · Sprint 5 cerrado · backend HU-001 a HU-020 completado · HU-021 Web Done · HU-022 con cierre técnico completado.</x:v>
+        <x:v>Versión 1.6 · Fecha de corte: 21-09-2026 · Sprint 6 cerrado · backend HU-001 a HU-020 completado · HU-021 a HU-024 Done.</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -1250,104 +1199,104 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="72" customHeight="1">
-      <x:c r="A10" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>58</x:v>
+      <x:c r="A10" s="1" t="str">
+        <x:v>R0.6</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="str">
+        <x:v>Sprint 6</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="str">
+        <x:v>Motor de reasignación y notificaciones internas</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="str">
+        <x:v>Candidatos, ranking, ofertas, aceptación/rechazo, expiración automática, continuidad y centro de notificaciones</x:v>
       </x:c>
       <x:c r="E10" s="1" t="str">
         <x:v>Completo</x:v>
       </x:c>
       <x:c r="F10" s="1" t="str">
-        <x:v>Backend HU-009/010/011/016/018 implementado. HU-022 Web completada con GET /reassignments/offers/me, ruta /ofertas, expiresAt real, aceptación/rechazo y estados finales. Validación: Web 71/71, pruebas enfocadas 10/10, E2E reasignaciones 20/20 y prueba manual de expiración/ACCEPT/REJECT PASS.</x:v>
+        <x:v>HU-009/010/011/016/018 backend; HU-022 Web ofertas; HU-023 expiración automática (PR #96, merge 109b1c9); HU-024 notificaciones internas (PR #99, merge b1bff30). Validación automática y manual PASS.</x:v>
       </x:c>
       <x:c r="G10" s="1" t="str">
-        <x:v>Motor de reasignación y flujo Web disponibles y validados de punta a punta, manteniendo backend como fuente de verdad.</x:v>
+        <x:v>Motor de reasignación completo, expiración persistente, continuidad segura y notificaciones internas disponibles de punta a punta</x:v>
       </x:c>
       <x:c r="H10" s="1" t="str">
-        <x:v>Integrar feat/web-reassignment-offers a main y actualizar la evidencia visual final del Kanban.</x:v>
+        <x:v>Mantener evidencia Scrum y revisar el cierre de la Web de usuario frente al alcance/bocetos antes de iniciar Desktop.</x:v>
       </x:c>
       <x:c r="I10" s="4" t="str">
-        <x:v>HU-009/010/011/016/018 backend Done; HU-021 Done; apps/web y entorno local estabilizados.</x:v>
+        <x:v>HU-009/010/011/016/018; apps/web; runner de expiración; Notification; PostgreSQL</x:v>
       </x:c>
       <x:c r="J10" s="4" t="str">
-        <x:v>Sprint 6 cerrado técnicamente. HU-022 queda lista para commit/PR/merge; ACCEPT transfirió la cita existente y REJECT no generó cita para el destinatario.</x:v>
+        <x:v>Sprint 6 cerrado. RF-029/RF-030/RF-034 quedan cubiertos. El backend continúa siendo fuente de verdad y las notificaciones externas permanecen fuera de alcance.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="72" customHeight="1">
-      <x:c r="A11" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>62</x:v>
+      <x:c r="A11" s="1" t="str">
+        <x:v>R0.7</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="str">
+        <x:v>Sprint 7</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="str">
+        <x:v>Aplicación institucional, operación y reportes</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="str">
+        <x:v>Fundación Tauri, agenda operativa, administración, asistencia, supervisión de reasignaciones, reportes y auditoría</x:v>
       </x:c>
       <x:c r="E11" s="1" t="str">
         <x:v>Parcial</x:v>
       </x:c>
       <x:c r="F11" s="1" t="str">
-        <x:v>Backend de reportes (HU-019) y auditoría (HU-020) implementado y mergeado; interfaces institucionales y aplicación Tauri aún pendientes.</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>Backend HU-012/013/014/015/016/017/018/019/020 implementado. Interfaces institucionales y apps/desktop todavía pendientes.</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="str">
+        <x:v>Aplicación de escritorio consume API y permite la operación institucional principal</x:v>
       </x:c>
       <x:c r="H11" s="1" t="str">
-        <x:v>Completar interfaces administrativas, agenda/asistencia, reportes/auditoría Web y luego Tauri.</x:v>
-      </x:c>
-      <x:c r="I11" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>Crear apps/desktop y conectar progresivamente las capacidades administrativas existentes.</x:v>
+      </x:c>
+      <x:c r="I11" s="4" t="str">
+        <x:v>APIs institucionales, RBAC, contexto, agenda, reportes y auditoría</x:v>
       </x:c>
       <x:c r="J11" s="4" t="str">
-        <x:v>Las capacidades backend de gestión ya existen; falta consolidar su experiencia institucional en Web/desktop.</x:v>
+        <x:v>El backend institucional ya existe. El siguiente trabajo se concentra en experiencia institucional, no en duplicar lógica de negocio.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="72" customHeight="1">
-      <x:c r="A12" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B12" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>69</x:v>
+      <x:c r="A12" s="1" t="str">
+        <x:v>R1.0</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="str">
+        <x:v>Sprint 8</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="str">
+        <x:v>Cierre MVP y preparación de defensa</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="str">
+        <x:v>Web + escritorio + backend + BD + Docker + pruebas + documentación + presentación</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="str">
+        <x:v>Pendiente</x:v>
       </x:c>
       <x:c r="F12" s="1" t="str">
-        <x:v>GitHub público; backend HU-001 a HU-020 implementado; HU-021 Web Done; HU-022 Web completada y validada técnicamente; entorno local reproducible con seed:dev/check:dev y tooling seed:reassignment-demo.</x:v>
-      </x:c>
-      <x:c r="G12" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>GitHub público; backend HU-001 a HU-020; HU-021 a HU-024 completadas; expiración automática y notificaciones internas operativas; entorno local reproducible.</x:v>
+      </x:c>
+      <x:c r="G12" s="1" t="str">
+        <x:v>MVP end-to-end demostrable y entregables académicos completos</x:v>
       </x:c>
       <x:c r="H12" s="1" t="str">
-        <x:v>Interfaces institucionales; Tauri; Docker; UML/ER final; pruebas de seguridad/rendimiento; documentación académica y defensa.</x:v>
-      </x:c>
-      <x:c r="I12" s="4" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="J12" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>Cerrar Web de usuario; Desktop institucional; integraciones externas seleccionadas; Docker; OpenAPI; seguridad/rendimiento; documentación y defensa.</x:v>
+      </x:c>
+      <x:c r="I12" s="4" t="str">
+        <x:v>Cierre de Sprints anteriores</x:v>
+      </x:c>
+      <x:c r="J12" s="4" t="str">
+        <x:v>Release académica final del proyecto.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="s">
-        <x:v>73</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B15" s="12"/>
       <x:c r="C15" s="12"/>
@@ -1364,39 +1313,39 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="20" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C16" s="20" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="D16" s="20" t="s">
-        <x:v>75</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E16" s="20" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F16" s="20" t="s">
-        <x:v>76</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G16" s="20" t="s">
-        <x:v>69</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H16" s="20" t="s">
-        <x:v>77</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I16" s="20" t="s">
-        <x:v>78</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J16" s="20" t="s">
-        <x:v>79</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="142.5">
       <x:c r="A17" s="21" t="s">
-        <x:v>80</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B17" s="21" t="s">
-        <x:v>81</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C17" s="22"/>
       <x:c r="D17" s="22"/>
@@ -2417,7 +2366,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ba09f8707084c39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f8ccf0b19274b1f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2436,7 +2385,7 @@
   <x:sheetData>
     <x:row r="1" ht="20.25">
       <x:c r="A1" s="14" t="str">
-        <x:v>CITAJUSTA — RESUMEN DEL RELEASE PLAN — ACTUALIZADO 20-09-2026</x:v>
+        <x:v>CITAJUSTA — RESUMEN DEL RELEASE PLAN — ACTUALIZADO 21-09-2026</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -2446,17 +2395,17 @@
     </x:row>
     <x:row r="3" ht="15">
       <x:c r="A3" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="5"/>
       <x:c r="D3" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F3" s="5"/>
     </x:row>
@@ -2562,7 +2511,7 @@
         <x:v>Fecha de corte</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>20-09-2026</x:v>
+        <x:v>21-09-2026</x:v>
       </x:c>
       <x:c r="C10" s="5"/>
       <x:c r="D10" s="5"/>
@@ -2579,7 +2528,7 @@
     </x:row>
     <x:row r="12" ht="15">
       <x:c r="A12" s="15" t="s">
-        <x:v>86</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B12" s="9"/>
       <x:c r="C12" s="9"/>
@@ -2592,7 +2541,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
         <x:v>12</x:v>
@@ -2601,10 +2550,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F13" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2621,10 +2570,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="E14" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F14" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2641,10 +2590,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F15" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2661,10 +2610,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F16" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="28.5">
@@ -2672,7 +2621,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B17" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C17" s="4" t="s">
         <x:v>51</x:v>
@@ -2688,14 +2637,14 @@
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B18" s="4" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C18" s="4" t="s">
-        <x:v>56</x:v>
+      <x:c r="A18" s="4" t="str">
+        <x:v>R0.6</x:v>
+      </x:c>
+      <x:c r="B18" s="4" t="str">
+        <x:v>Reasignación + notificaciones</x:v>
+      </x:c>
+      <x:c r="C18" s="4" t="str">
+        <x:v>Sprint 6</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
         <x:v>Completo</x:v>
@@ -2704,18 +2653,18 @@
         <x:v>→</x:v>
       </x:c>
       <x:c r="F18" s="4" t="str">
-        <x:v>Backend + HU-022 Web completados y validados</x:v>
+        <x:v>HU-022/023/024 Done · RF-029/030/034 cubiertos</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B19" s="4" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C19" s="4" t="s">
-        <x:v>60</x:v>
+      <x:c r="A19" s="4" t="str">
+        <x:v>R0.7</x:v>
+      </x:c>
+      <x:c r="B19" s="4" t="str">
+        <x:v>Aplicación institucional</x:v>
+      </x:c>
+      <x:c r="C19" s="4" t="str">
+        <x:v>Sprint 7</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
         <x:v>Parcial</x:v>
@@ -2724,18 +2673,18 @@
         <x:v>→</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
-        <x:v>HU-019/HU-020 backend Done · UI/Tauri pendiente</x:v>
+        <x:v>Backend institucional Done · UI/Tauri pendiente</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="42.75">
       <x:c r="A20" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B20" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -2757,7 +2706,7 @@
     </x:row>
     <x:row r="22" ht="15.75" customHeight="1">
       <x:c r="A22" s="23" t="s">
-        <x:v>97</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B22" s="23"/>
       <x:c r="C22" s="23"/>
@@ -2767,7 +2716,7 @@
     </x:row>
     <x:row r="23" ht="72" customHeight="1">
       <x:c r="A23" s="24" t="str">
-        <x:v>Backend HU-001 a HU-020 completado. HU-021 Web de lista de espera/preferencias fue mergeada mediante PR #89. HU-022 Web de ofertas/reasignación alcanzó cierre técnico con 71/71 pruebas Web, 10/10 pruebas enfocadas, 20/20 E2E reales y validación manual de expiración, ACCEPT y REJECT. Próximo foco: integrar la rama a main y continuar interfaces institucionales.</x:v>
+        <x:v>Backend HU-001 a HU-020 completado. HU-021/022 cerraron la experiencia Web de waitlist/ofertas; HU-023 agregó expiración automática y continuidad segura; HU-024 agregó notificaciones internas persistentes y centro Web. PR #96 y #99 ya fueron mergeadas a main. Próximo foco: cerrar la Web de usuario frente al alcance y comenzar la aplicación institucional de escritorio.</x:v>
       </x:c>
       <x:c r="B23" s="24"/>
       <x:c r="C23" s="24"/>
@@ -3781,6 +3730,6 @@
     <x:mergeCell ref="A23:F26"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reed7d67a3e34431f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddb6af87af06483f"/>
 </x:worksheet>
 </file>